--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566895945</v>
+        <v>46157.93094818937</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93094818937</v>
+        <v>46157.9317106847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9317106847</v>
+        <v>46157.93398726745</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398726745</v>
+        <v>46157.93716467002</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716467002</v>
+        <v>46158.2821508444</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821508444</v>
+        <v>46158.29676577458</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676577458</v>
+        <v>46158.29813170835</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29813170835</v>
+        <v>46158.33386040722</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33386040722</v>
+        <v>46158.36855813216</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855813216</v>
+        <v>46158.3728653402</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
